--- a/data/Rivers/env_swed_riv_def.xlsx
+++ b/data/Rivers/env_swed_riv_def.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20409"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugirona-my.sharepoint.com/personal/u4001106_udg_edu/Documents/tesi/WP1 NATs/NAT_FunMetaNET/data/Rivers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anna\OneDrive - Universitat de Girona\tesi\WP1 NATs\NAT_FunMetaNET\data\Rivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C327B3A4-4272-487C-BD91-E2EF7D87ABE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{C327B3A4-4272-487C-BD91-E2EF7D87ABE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{08A7108F-5884-465D-AB07-31035D09FF14}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{85C0D3EC-8BAD-435A-8768-A95FCA2A9839}"/>
   </bookViews>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Virån</t>
-  </si>
-  <si>
-    <t>Vingån, Vingäng</t>
   </si>
   <si>
     <t>Viepsajåkkå</t>
@@ -180,9 +177,6 @@
     <t>Blankan Ryerna</t>
   </si>
   <si>
-    <t>Arån Arålund</t>
-  </si>
-  <si>
     <t>water_temp (°C)</t>
   </si>
   <si>
@@ -202,6 +196,12 @@
   </si>
   <si>
     <t>site</t>
+  </si>
+  <si>
+    <t>Vingån</t>
+  </si>
+  <si>
+    <t>Arån</t>
   </si>
 </sst>
 </file>
@@ -579,30 +579,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -648,7 +648,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -855,7 +855,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
@@ -878,7 +878,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>2007</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>2008</v>
@@ -924,7 +924,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>2009</v>
@@ -947,7 +947,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>2010</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>2011</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>2012</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>2013</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>2014</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>2015</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23">
         <v>2016</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>2017</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25">
         <v>2018</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
@@ -1384,7 +1384,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
         <v>0</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>3</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
         <v>2</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
         <v>7</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
         <v>6</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
         <v>5</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
         <v>3</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
         <v>2</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
         <v>9</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
         <v>7</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B68" t="s">
         <v>6</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" t="s">
         <v>5</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
         <v>3</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B73" t="s">
         <v>0</v>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B76" t="s">
         <v>10</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
         <v>7</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B80" t="s">
         <v>6</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s">
         <v>5</v>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B83" t="s">
         <v>3</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B84" t="s">
         <v>2</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B85" t="s">
         <v>0</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B88" t="s">
         <v>10</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -2626,7 +2626,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B90" t="s">
         <v>8</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B91" t="s">
         <v>7</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
         <v>6</v>
@@ -2695,7 +2695,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
         <v>5</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
         <v>3</v>
@@ -2764,7 +2764,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
         <v>2</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B99" t="s">
         <v>11</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B101" t="s">
         <v>9</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B102" t="s">
         <v>8</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B103" t="s">
         <v>7</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B104" t="s">
         <v>6</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B105" t="s">
         <v>5</v>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B107" t="s">
         <v>3</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B108" t="s">
         <v>2</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B109" t="s">
         <v>0</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B111" t="s">
         <v>11</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B112" t="s">
         <v>10</v>
@@ -3155,7 +3155,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B113" t="s">
         <v>9</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B116" t="s">
         <v>6</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B117" t="s">
         <v>5</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B119" t="s">
         <v>3</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B120" t="s">
         <v>2</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B121" t="s">
         <v>0</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B123" t="s">
         <v>11</v>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B124" t="s">
         <v>10</v>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B125" t="s">
         <v>9</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B126" t="s">
         <v>8</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B127" t="s">
         <v>7</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B128" t="s">
         <v>6</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B129" t="s">
         <v>5</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B131" t="s">
         <v>3</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B132" t="s">
         <v>2</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B133" t="s">
         <v>0</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B134" t="s">
         <v>12</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B135" t="s">
         <v>11</v>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B136" t="s">
         <v>10</v>
@@ -3707,7 +3707,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B137" t="s">
         <v>9</v>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B138" t="s">
         <v>8</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B140" t="s">
         <v>6</v>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B141" t="s">
         <v>5</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B142" t="s">
         <v>4</v>
@@ -3845,7 +3845,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B143" t="s">
         <v>3</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B144" t="s">
         <v>2</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B145" t="s">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B146" t="s">
         <v>12</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B147" t="s">
         <v>11</v>
@@ -3960,7 +3960,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B148" t="s">
         <v>10</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B149" t="s">
         <v>9</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B150" t="s">
         <v>8</v>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B151" t="s">
         <v>7</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B152" t="s">
         <v>6</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B153" t="s">
         <v>5</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B154" t="s">
         <v>4</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B155" t="s">
         <v>3</v>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B156" t="s">
         <v>2</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B157" t="s">
         <v>0</v>
@@ -4190,7 +4190,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B158" t="s">
         <v>12</v>
@@ -4213,7 +4213,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B159" t="s">
         <v>11</v>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B160" t="s">
         <v>10</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B161" t="s">
         <v>9</v>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B162" t="s">
         <v>8</v>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B163" t="s">
         <v>7</v>
@@ -4328,7 +4328,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B164" t="s">
         <v>6</v>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B165" t="s">
         <v>5</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B166" t="s">
         <v>4</v>
@@ -4397,7 +4397,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B167" t="s">
         <v>3</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B168" t="s">
         <v>2</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B169" t="s">
         <v>0</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B170" t="s">
         <v>12</v>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B171" t="s">
         <v>11</v>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B172" t="s">
         <v>10</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B173" t="s">
         <v>9</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B174" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B175" t="s">
         <v>7</v>
@@ -4604,7 +4604,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B176" t="s">
         <v>6</v>
@@ -4627,7 +4627,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B177" t="s">
         <v>5</v>
@@ -4650,7 +4650,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B178" t="s">
         <v>4</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B179" t="s">
         <v>3</v>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B180" t="s">
         <v>2</v>
@@ -4719,7 +4719,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B181" t="s">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B182" t="s">
         <v>12</v>
@@ -4765,7 +4765,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B183" t="s">
         <v>11</v>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B184" t="s">
         <v>10</v>
@@ -4811,7 +4811,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B185" t="s">
         <v>9</v>
@@ -4834,7 +4834,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B186" t="s">
         <v>8</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B187" t="s">
         <v>7</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B188" t="s">
         <v>6</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B189" t="s">
         <v>5</v>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B190" t="s">
         <v>4</v>
@@ -4949,7 +4949,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B191" t="s">
         <v>3</v>
@@ -4972,7 +4972,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B192" t="s">
         <v>2</v>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B193" t="s">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B194" t="s">
         <v>12</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B195" t="s">
         <v>11</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B196" t="s">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B197" t="s">
         <v>9</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B198" t="s">
         <v>8</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B199" t="s">
         <v>7</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B200" t="s">
         <v>6</v>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B201" t="s">
         <v>5</v>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B202" t="s">
         <v>4</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B203" t="s">
         <v>3</v>
@@ -5248,7 +5248,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B204" t="s">
         <v>2</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B205" t="s">
         <v>0</v>
@@ -5294,7 +5294,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B206" t="s">
         <v>12</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B207" t="s">
         <v>11</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B208" t="s">
         <v>10</v>
@@ -5363,7 +5363,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B209" t="s">
         <v>9</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B210" t="s">
         <v>8</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B211" t="s">
         <v>7</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B212" t="s">
         <v>6</v>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B213" t="s">
         <v>5</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B214" t="s">
         <v>4</v>
@@ -5501,7 +5501,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B215" t="s">
         <v>3</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B216" t="s">
         <v>2</v>
@@ -5547,7 +5547,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B217" t="s">
         <v>0</v>
@@ -5570,7 +5570,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B218" t="s">
         <v>12</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B219" t="s">
         <v>11</v>
@@ -5616,7 +5616,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B220" t="s">
         <v>10</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B221" t="s">
         <v>9</v>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B222" t="s">
         <v>8</v>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B223" t="s">
         <v>7</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B224" t="s">
         <v>6</v>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B225" t="s">
         <v>5</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B226" t="s">
         <v>4</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B227" t="s">
         <v>3</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B228" t="s">
         <v>2</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B229" t="s">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B230" t="s">
         <v>12</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B231" t="s">
         <v>11</v>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B232" t="s">
         <v>10</v>
@@ -5915,7 +5915,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B233" t="s">
         <v>9</v>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B234" t="s">
         <v>8</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B235" t="s">
         <v>7</v>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B236" t="s">
         <v>6</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B237" t="s">
         <v>5</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B238" t="s">
         <v>4</v>
@@ -6053,7 +6053,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B239" t="s">
         <v>3</v>
@@ -6076,7 +6076,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B240" t="s">
         <v>2</v>
@@ -6099,7 +6099,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B241" t="s">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B242" t="s">
         <v>12</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B243" t="s">
         <v>11</v>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B244" t="s">
         <v>10</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B245" t="s">
         <v>9</v>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B246" t="s">
         <v>8</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B247" t="s">
         <v>7</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B248" t="s">
         <v>6</v>
@@ -6283,7 +6283,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B249" t="s">
         <v>5</v>
@@ -6306,7 +6306,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B250" t="s">
         <v>4</v>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B251" t="s">
         <v>3</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B252" t="s">
         <v>2</v>
@@ -6375,7 +6375,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B253" t="s">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B254" t="s">
         <v>12</v>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B255" t="s">
         <v>11</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B256" t="s">
         <v>10</v>
@@ -6467,7 +6467,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B257" t="s">
         <v>9</v>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B258" t="s">
         <v>8</v>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B259" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B260" t="s">
         <v>6</v>
@@ -6559,7 +6559,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B261" t="s">
         <v>5</v>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B262" t="s">
         <v>4</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B263" t="s">
         <v>3</v>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B264" t="s">
         <v>2</v>
@@ -6651,7 +6651,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B265" t="s">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B266" t="s">
         <v>12</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B267" t="s">
         <v>11</v>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B268" t="s">
         <v>10</v>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B269" t="s">
         <v>9</v>
@@ -6766,7 +6766,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B270" t="s">
         <v>8</v>
@@ -6789,7 +6789,7 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B271" t="s">
         <v>7</v>
@@ -6812,7 +6812,7 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B272" t="s">
         <v>6</v>
@@ -6835,7 +6835,7 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B273" t="s">
         <v>5</v>
@@ -6858,7 +6858,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B274" t="s">
         <v>4</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B275" t="s">
         <v>3</v>
@@ -6904,7 +6904,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B276" t="s">
         <v>2</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B277" t="s">
         <v>0</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B278" t="s">
         <v>12</v>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B279" t="s">
         <v>11</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B280" t="s">
         <v>10</v>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B281" t="s">
         <v>9</v>
@@ -7042,7 +7042,7 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B282" t="s">
         <v>8</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B283" t="s">
         <v>7</v>
@@ -7088,7 +7088,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B284" t="s">
         <v>6</v>
@@ -7111,7 +7111,7 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B285" t="s">
         <v>5</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B286" t="s">
         <v>4</v>
@@ -7157,7 +7157,7 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B287" t="s">
         <v>3</v>
@@ -7180,7 +7180,7 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B288" t="s">
         <v>2</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B289" t="s">
         <v>0</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B290" t="s">
         <v>12</v>
@@ -7249,7 +7249,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B291" t="s">
         <v>11</v>
@@ -7272,7 +7272,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B292" t="s">
         <v>10</v>
@@ -7295,7 +7295,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B293" t="s">
         <v>9</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B294" t="s">
         <v>8</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B295" t="s">
         <v>7</v>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B296" t="s">
         <v>6</v>
@@ -7387,7 +7387,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B297" t="s">
         <v>5</v>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B298" t="s">
         <v>4</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B299" t="s">
         <v>3</v>
@@ -7456,7 +7456,7 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B300" t="s">
         <v>2</v>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B301" t="s">
         <v>0</v>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B302" t="s">
         <v>12</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B303" t="s">
         <v>11</v>
@@ -7548,7 +7548,7 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B304" t="s">
         <v>10</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B305" t="s">
         <v>9</v>
@@ -7594,7 +7594,7 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B306" t="s">
         <v>8</v>
@@ -7617,7 +7617,7 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B307" t="s">
         <v>7</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B308" t="s">
         <v>6</v>
@@ -7663,7 +7663,7 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B309" t="s">
         <v>5</v>
@@ -7686,7 +7686,7 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B310" t="s">
         <v>4</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B311" t="s">
         <v>3</v>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B312" t="s">
         <v>2</v>
@@ -7755,7 +7755,7 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B313" t="s">
         <v>0</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B314" t="s">
         <v>12</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B315" t="s">
         <v>11</v>
@@ -7824,7 +7824,7 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B316" t="s">
         <v>10</v>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B317" t="s">
         <v>9</v>
@@ -7870,7 +7870,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B318" t="s">
         <v>8</v>
@@ -7893,7 +7893,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B319" t="s">
         <v>7</v>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B320" t="s">
         <v>6</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B321" t="s">
         <v>5</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B322" t="s">
         <v>4</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B323" t="s">
         <v>3</v>
@@ -8008,7 +8008,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B324" t="s">
         <v>2</v>
@@ -8031,7 +8031,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B325" t="s">
         <v>0</v>
@@ -8054,7 +8054,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B326" t="s">
         <v>12</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B327" t="s">
         <v>11</v>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B328" t="s">
         <v>10</v>
@@ -8123,7 +8123,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B329" t="s">
         <v>9</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B330" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B331" t="s">
         <v>7</v>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B332" t="s">
         <v>6</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B333" t="s">
         <v>5</v>
@@ -8238,7 +8238,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B334" t="s">
         <v>4</v>
@@ -8261,7 +8261,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B335" t="s">
         <v>3</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B336" t="s">
         <v>2</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B337" t="s">
         <v>0</v>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B338" t="s">
         <v>12</v>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B339" t="s">
         <v>11</v>
@@ -8376,7 +8376,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B340" t="s">
         <v>10</v>
@@ -8399,7 +8399,7 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B341" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B342" t="s">
         <v>8</v>
@@ -8445,7 +8445,7 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B343" t="s">
         <v>7</v>
@@ -8468,7 +8468,7 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B344" t="s">
         <v>6</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B345" t="s">
         <v>5</v>
@@ -8514,7 +8514,7 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B346" t="s">
         <v>4</v>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B347" t="s">
         <v>3</v>
@@ -8560,7 +8560,7 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B348" t="s">
         <v>2</v>
@@ -8583,7 +8583,7 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B349" t="s">
         <v>0</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B350" t="s">
         <v>12</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B351" t="s">
         <v>11</v>
@@ -8652,7 +8652,7 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B352" t="s">
         <v>10</v>
@@ -8675,7 +8675,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B353" t="s">
         <v>9</v>
@@ -8698,7 +8698,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B354" t="s">
         <v>8</v>
@@ -8721,7 +8721,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B355" t="s">
         <v>7</v>
@@ -8744,7 +8744,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B356" t="s">
         <v>6</v>
@@ -8767,7 +8767,7 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B357" t="s">
         <v>5</v>
@@ -8790,7 +8790,7 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B358" t="s">
         <v>4</v>
@@ -8813,7 +8813,7 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B359" t="s">
         <v>3</v>
@@ -8836,7 +8836,7 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B360" t="s">
         <v>2</v>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B361" t="s">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B362" t="s">
         <v>12</v>
@@ -8905,7 +8905,7 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B363" t="s">
         <v>11</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B364" t="s">
         <v>10</v>
@@ -8951,7 +8951,7 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B365" t="s">
         <v>9</v>
@@ -8974,7 +8974,7 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B366" t="s">
         <v>8</v>
@@ -8997,7 +8997,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B367" t="s">
         <v>7</v>
@@ -9020,7 +9020,7 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B368" t="s">
         <v>6</v>
@@ -9043,7 +9043,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B369" t="s">
         <v>5</v>
@@ -9066,7 +9066,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B370" t="s">
         <v>4</v>
@@ -9089,7 +9089,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B371" t="s">
         <v>3</v>
@@ -9112,7 +9112,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B372" t="s">
         <v>2</v>
@@ -9135,7 +9135,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B373" t="s">
         <v>0</v>
@@ -9158,7 +9158,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B374" t="s">
         <v>12</v>
@@ -9181,7 +9181,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B375" t="s">
         <v>11</v>
@@ -9204,7 +9204,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B376" t="s">
         <v>10</v>
@@ -9227,7 +9227,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B377" t="s">
         <v>9</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B378" t="s">
         <v>8</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B379" t="s">
         <v>7</v>
@@ -9296,7 +9296,7 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B380" t="s">
         <v>6</v>
@@ -9319,7 +9319,7 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B381" t="s">
         <v>5</v>
@@ -9342,7 +9342,7 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B382" t="s">
         <v>4</v>
@@ -9365,7 +9365,7 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B383" t="s">
         <v>3</v>
@@ -9388,7 +9388,7 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B384" t="s">
         <v>2</v>
@@ -9411,7 +9411,7 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B385" t="s">
         <v>0</v>
@@ -9434,7 +9434,7 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B386" t="s">
         <v>12</v>
@@ -9457,7 +9457,7 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B387" t="s">
         <v>11</v>
@@ -9480,7 +9480,7 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B388" t="s">
         <v>10</v>
@@ -9503,7 +9503,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B390" t="s">
         <v>8</v>
@@ -9549,7 +9549,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B391" t="s">
         <v>7</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B392" t="s">
         <v>6</v>
@@ -9595,7 +9595,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B393" t="s">
         <v>5</v>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B394" t="s">
         <v>4</v>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B395" t="s">
         <v>3</v>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B396" t="s">
         <v>2</v>
@@ -9687,7 +9687,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B397" t="s">
         <v>0</v>
@@ -9710,7 +9710,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B398" t="s">
         <v>12</v>
@@ -9733,7 +9733,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B399" t="s">
         <v>11</v>
@@ -9756,7 +9756,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B400" t="s">
         <v>10</v>
@@ -9779,7 +9779,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B401" t="s">
         <v>9</v>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B402" t="s">
         <v>8</v>
@@ -9825,7 +9825,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B403" t="s">
         <v>7</v>
@@ -9848,7 +9848,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B404" t="s">
         <v>6</v>
@@ -9871,7 +9871,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B405" t="s">
         <v>5</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B406" t="s">
         <v>4</v>
@@ -9917,7 +9917,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B407" t="s">
         <v>3</v>
@@ -9940,7 +9940,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B408" t="s">
         <v>2</v>
@@ -9963,7 +9963,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B409" t="s">
         <v>0</v>
@@ -9986,7 +9986,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B410" t="s">
         <v>12</v>
@@ -10009,7 +10009,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B411" t="s">
         <v>11</v>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B412" t="s">
         <v>10</v>
@@ -10055,7 +10055,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B413" t="s">
         <v>9</v>
@@ -10078,7 +10078,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B414" t="s">
         <v>8</v>
@@ -10101,7 +10101,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B415" t="s">
         <v>7</v>
@@ -10124,7 +10124,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B416" t="s">
         <v>6</v>
@@ -10147,7 +10147,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B417" t="s">
         <v>5</v>
@@ -10170,7 +10170,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B418" t="s">
         <v>4</v>
@@ -10193,7 +10193,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B419" t="s">
         <v>3</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B420" t="s">
         <v>2</v>
@@ -10239,7 +10239,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B421" t="s">
         <v>0</v>
@@ -10262,7 +10262,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B422" t="s">
         <v>12</v>
@@ -10285,7 +10285,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B423" t="s">
         <v>11</v>
@@ -10308,7 +10308,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B424" t="s">
         <v>10</v>
@@ -10331,7 +10331,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B425" t="s">
         <v>9</v>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B426" t="s">
         <v>8</v>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B427" t="s">
         <v>7</v>
@@ -10400,7 +10400,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B428" t="s">
         <v>6</v>
@@ -10423,7 +10423,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B429" t="s">
         <v>5</v>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B430" t="s">
         <v>4</v>
@@ -10469,7 +10469,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B431" t="s">
         <v>3</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B432" t="s">
         <v>2</v>
@@ -10515,7 +10515,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B433" t="s">
         <v>0</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B434" t="s">
         <v>12</v>
@@ -10561,7 +10561,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B435" t="s">
         <v>11</v>
@@ -10584,7 +10584,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B436" t="s">
         <v>10</v>
@@ -10607,7 +10607,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B437" t="s">
         <v>9</v>
@@ -10630,7 +10630,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B438" t="s">
         <v>8</v>
@@ -10653,7 +10653,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B439" t="s">
         <v>7</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B440" t="s">
         <v>6</v>
@@ -10699,7 +10699,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B441" t="s">
         <v>5</v>
@@ -10722,7 +10722,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B442" t="s">
         <v>4</v>
@@ -10745,7 +10745,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B443" t="s">
         <v>3</v>
@@ -10768,7 +10768,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B444" t="s">
         <v>2</v>
@@ -10791,7 +10791,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B445" t="s">
         <v>0</v>
@@ -11375,6 +11375,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b8aad7d3-4569-465e-b6db-b00f3847ad08" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CEBE5EA080DAB6418FDF4B171D3DCB62" ma:contentTypeVersion="15" ma:contentTypeDescription="Crea un document nou" ma:contentTypeScope="" ma:versionID="14be2585f0750c70ac37da64bd5e341f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b8aad7d3-4569-465e-b6db-b00f3847ad08" xmlns:ns4="7a05725b-432a-4f4b-8a80-b3c0b821d7de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8d7b829918895e99ee2c465c2730c87" ns3:_="" ns4:_="">
     <xsd:import namespace="b8aad7d3-4569-465e-b6db-b00f3847ad08"/>
@@ -11607,24 +11624,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B600B78D-8ADB-49AE-8704-3793757D1C59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b8aad7d3-4569-465e-b6db-b00f3847ad08" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E36177C-51D2-480C-B81E-3C083FB8AC0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7a05725b-432a-4f4b-8a80-b3c0b821d7de"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b8aad7d3-4569-465e-b6db-b00f3847ad08"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41F5AFB4-95D9-436B-8041-2BE429937BB3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11641,29 +11666,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B600B78D-8ADB-49AE-8704-3793757D1C59}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E36177C-51D2-480C-B81E-3C083FB8AC0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7a05725b-432a-4f4b-8a80-b3c0b821d7de"/>
-    <ds:schemaRef ds:uri="b8aad7d3-4569-465e-b6db-b00f3847ad08"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>